--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$P$96</definedName>
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-21 11:00</t>
+          <t>2026-10-22 00:26</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-22 00:26</t>
+          <t>2026-10-22 06:29</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -31,9 +31,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Nunito"/>
+      <name val="Montserrat"/>
       <b val="1"/>
-      <color rgb="00F7F4FC"/>
+      <color rgb="00FFF9F2"/>
       <sz val="11"/>
     </font>
     <font>
@@ -41,13 +41,13 @@
       <sz val="10"/>
     </font>
     <font>
-      <name val="Nunito"/>
+      <name val="Montserrat"/>
       <b val="1"/>
       <sz val="13"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00F7F4FC"/>
+      <color rgb="00FFF9F2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -59,7 +59,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00322D5B"/>
+        <fgColor rgb="004B4141"/>
       </patternFill>
     </fill>
   </fills>
@@ -73,7 +73,7 @@
     </border>
     <border>
       <bottom style="thin">
-        <color rgb="00E6DFF3"/>
+        <color rgb="00E9D9C8"/>
       </bottom>
     </border>
   </borders>
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-22 06:29</t>
+          <t>2026-10-22 12:30</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-22 12:30</t>
+          <t>2026-10-22 18:24</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-22 18:24</t>
+          <t>2026-10-23 00:27</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-23 00:27</t>
+          <t>2026-10-23 06:28</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-23 06:28</t>
+          <t>2026-10-23 12:24</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-23 12:24</t>
+          <t>2026-10-23 18:24</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -33,7 +33,7 @@
     <font>
       <name val="Montserrat"/>
       <b val="1"/>
-      <color rgb="00FFF9F2"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
@@ -47,7 +47,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFF9F2"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="3">
@@ -59,7 +59,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004B4141"/>
+        <fgColor rgb="001F1F1F"/>
       </patternFill>
     </fill>
   </fills>
@@ -73,7 +73,7 @@
     </border>
     <border>
       <bottom style="thin">
-        <color rgb="00E9D9C8"/>
+        <color rgb="00E6E8EB"/>
       </bottom>
     </border>
   </borders>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>AZUL, BEIZ, LILA, NEGRO, ROSADO, BLANCO HUESO, BLANCO, ROJO</t>
+          <t>AZUL, LILA, NEGRO, ROSADO, BLANCO HUESO, BLANCO</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="P26" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>VAQUITA MORADA, AVOCADO FUCSIA, STICH MORADO, KOALA, OSO LOTSO, MINNIE, CERDITO FUCSIA, CAPIBARA CAFE, VAQUITA NEGRA, MICKEY NEGRO, AVOCADO, BEARS</t>
+          <t>STICH MORADO, KOALA, OSO LOTSO, MINNIE, CAPIBARA CAFE, VAQUITA NEGRA, MICKEY NEGRO, AVOCADO, BEARS</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -2766,11 +2766,11 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/qqwsrxvr1ic_1789406839500.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/dvn5kd4fejc_1789406841873.webp</t>
         </is>
       </c>
       <c r="P36" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>SANTA, SANTA CARICATURAS, SANTA TRINEO</t>
+          <t>SANTA, SANTA TRINEO</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="P37" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>VAQUITA ROSA, PANTERA ROSA, SNOOPY FLOR, VAQUITA MOÑO, WINE POOH, ELMO, DONALD, GARFIELD, ELEFANTE, PUCCA, GATICA, OSA MOÑO, OSO, CUTR PUPPY, GATICA MOÑO, CUTE SWAN, CERDITO, PIOLIN</t>
+          <t>VAQUITA ROSA, PANTERA ROSA, SNOOPY FLOR, VAQUITA MOÑO, WINE POOH, ELMO, DONALD, GARFIELD, ELEFANTE, PUCCA, GATICA, OSA MOÑO, OSO, CUTR PUPPY, GATICA MOÑO, CUTE SWAN, CERDITO</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="P38" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>KITTY, CAPIBARA, LABUBU, Oso lottso, PANTERA ROSA, SNOOPY, CAPIBARA CAFE, JIRAFA TIERNA, HELLO KITTY, PATO DONALD</t>
+          <t>KITTY, CAPIBARA, LABUBU, Oso lottso, PANTERA ROSA, SNOOPY, CAPIBARA CAFE, JIRAFA TIERNA, PATO DONALD</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
         </is>
       </c>
       <c r="P55" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>CAPIBARA, VAQUITA MOO, DEISY, MAFALDA MORADO, OSO CARIÑOSO, MINNIE, HELLO KITTY</t>
+          <t>CAPIBARA, VAQUITA MOO, DEISY, MAFALDA MORADO, OSO CARIÑOSO, MINNIE</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4132,7 +4132,7 @@
         </is>
       </c>
       <c r="P57" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>OJOS, MINNIE, HELLO KITTY, OSO PANDA, STICH</t>
+          <t>OJOS, MINNIE, OSO PANDA, STICH</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -4632,7 +4632,7 @@
         </is>
       </c>
       <c r="P65" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>1003145115, RULERGS, OSO ANTIFAZ, COFFE, PRINCESA MARIO, DINO BEAR, GATO FRESA</t>
+          <t>PRINCESA MARIO, DINO BEAR, GATO FRESA</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -4888,11 +4888,11 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/q027f72zlv8_1784914996896.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/aeirxq4xmf_1789406213691.webp</t>
         </is>
       </c>
       <c r="P69" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>OSO LOTSO, POCHACO, CAPIBARA NARANJA, CINAMORROL, BURBUJA, 1002416596</t>
+          <t>POCHACO, CAPIBARA NARANJA, CINAMORROL, BURBUJA, 1002416596</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -5470,11 +5470,11 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/e0wxiek6bya_1784951657522.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/1pwd5aw4xvn_1784951658664.jpg</t>
         </is>
       </c>
       <c r="P78" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>HELLO KITTY, OSO LOTSO, MICKEY, PIOLIN, TIGERS, PINGUINOS, AVOCADO, CERDITO, CAPIBARA, BAMBI, PALETA LILA, BOB ESPONJA, CINAMORROL, MINNI FLOR, ELEFANTE, AVOCADO FUCSIA, BOB BONNY, STICH, CUTE, OSO PANDA, MAFALDA, PIOLIN AMARILLO, OVEJA NUVE, MY MELODDY, OSA</t>
+          <t>OSO LOTSO, MICKEY, HELLO KITTY, TIGERS, PINGUINOS, AVOCADO, CERDITO, CAPIBARA, BAMBI, PALETA LILA, BOB ESPONJA, CINAMORROL, MINNI FLOR, ELEFANTE, STICH, OSO PANDA, MAFALDA, OVEJA NUVE, MY MELODDY</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -6276,11 +6276,11 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/wq6vkaejj3f_1784922917937.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/jxcws9687y_1784922919118.jpg</t>
         </is>
       </c>
       <c r="P91" s="2" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="92">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-23 18:24</t>
+          <t>2026-10-23 20:42</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-23 20:42</t>
+          <t>2026-10-24 00:43</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -5691,10 +5691,10 @@
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>3</v>
+        <v>36000</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>2</v>
+        <v>26000</v>
       </c>
       <c r="I82" s="3" t="n">
         <v>1</v>
@@ -5749,7 +5749,7 @@
       <c r="E83" s="2" t="inlineStr"/>
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="3" t="n">
-        <v>3</v>
+        <v>36000</v>
       </c>
       <c r="H83" s="3" t="n"/>
       <c r="I83" s="3" t="n"/>
@@ -5803,10 +5803,10 @@
       <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="3" t="n">
-        <v>3</v>
+        <v>36000</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>2</v>
+        <v>26000</v>
       </c>
       <c r="I84" s="3" t="n">
         <v>1</v>
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-24 00:43</t>
+          <t>2026-10-24 06:32</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-24 06:32</t>
+          <t>2026-10-24 12:30</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-24 12:30</t>
+          <t>2026-10-24 18:26</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-24 18:26</t>
+          <t>2026-10-25 00:33</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25 00:33</t>
+          <t>2026-10-25 06:32</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25 06:32</t>
+          <t>2026-10-25 12:30</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25 12:30</t>
+          <t>2026-10-25 18:27</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25 18:27</t>
+          <t>2026-10-26 00:47</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-26 00:47</t>
+          <t>2026-10-26 06:42</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-26 06:42</t>
+          <t>2026-10-26 14:43</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -2496,7 +2496,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>AMARILLO, SALMON, ROSA, ROSADO, AZUL, LILA</t>
+          <t>AMARILLO, SALMON, AZUL, LILA</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="P32" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>TOTTO, WINNE POOH, WINNE POOH LILA</t>
+          <t>TOTTO, WINNE POOH</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="P74" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>MINNIE, DONAL Y DEISY, 1002612353, LABUBU CAFE, VAQUITA ESPACIAL, MICKEY, MINNIE AZUL, HELLO KITTY</t>
+          <t>DONAL Y DEISY, 1002612353, LABUBU CAFE, VAQUITA ESPACIAL, MICKEY, MINNIE AZUL, HELLO KITTY</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -5536,11 +5536,11 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/njirlp0s9_1784991741310.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/2i5ai5chp2u_1784991743787.jpg</t>
         </is>
       </c>
       <c r="P79" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>FUCSIA, ROJA, BEIZ, NEGRO, ROSA, BLANCO HUESO, AZUL TURQUI</t>
+          <t>ROJA, NEGRO, BLANCO HUESO</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -6210,11 +6210,11 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/w20s9ddim4r_1791399518651.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/lm6eiuewqld_1791399520169.webp</t>
         </is>
       </c>
       <c r="P90" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-26 14:43</t>
+          <t>2026-10-26 18:43</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-26 18:43</t>
+          <t>2026-10-27 00:37</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:37</t>
+          <t>2026-10-27 06:39</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 06:39</t>
+          <t>2026-10-27 12:40</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 12:40</t>
+          <t>2026-10-27 18:40</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 18:40</t>
+          <t>2026-10-28 00:47</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-28 00:47</t>
+          <t>2026-10-28 06:46</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-28 06:46</t>
+          <t>2026-10-28 12:47</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1004165238, 1004165237, 1004165236, 1004165235, 1004165234, 1004165233, 1004165232, 1004165231, 1004165230, 1004165229, 1004165228, 1004165227, 1004165226, 1004165225, 1004165224, 1004165218</t>
+          <t>1004165237, 1004165234, 1004165233, 1004165232, 1004165231, 1004165230, 1004165227, 1004165226, 1004165224, 1004165218</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1126,11 +1126,11 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/j7a765w02fc_1792168079354.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/g3gm0hniit5_1792168080708.webp</t>
         </is>
       </c>
       <c r="P10" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -3249,7 +3249,11 @@
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>2/4, 6/8, 10/12, 14/16</t>
+        </is>
+      </c>
       <c r="G44" s="3" t="n">
         <v>25000</v>
       </c>
@@ -3270,7 +3274,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>CINAMORROL, CERDITO, AVOCADO, STICH, BLANCA NIEVES, BOB ESPONJA, CAPIBARA, GUERRERAS KPOP, GATA MARIE, LILO Y STICH, PERRO MORADO, OSITA GLOBOS</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>TALLAS 2/4-6/8-10/12-14/16 TALLAJE NORMAL</t>
@@ -6660,7 +6668,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -6671,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-28 12:47</t>
+          <t>2026-10-28 18:43</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-28 18:43</t>
+          <t>2026-10-29 00:47</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 00:47</t>
+          <t>2026-10-29 06:48</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 06:48</t>
+          <t>2026-10-29 12:48</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 12:48</t>
+          <t>2026-10-29 18:45</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 18:45</t>
+          <t>2026-10-30 00:49</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -4774,17 +4774,17 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>23141b4f-2a7f-46ad-af38-1c09e3487a0a</t>
+          <t>f76a5f9c-6d1c-470d-9ad3-58f6c5a4fc8a</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>SET104</t>
+          <t>STP-002</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>SHORT ESQUELETO TALLA UNICA</t>
+          <t>SHORT TIRA PLUS</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Única</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="G68" s="3" t="n">
@@ -4820,37 +4820,37 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>STICH ROSADO, STICH MORADO, STICH AZUL, STICH BLANCO</t>
+          <t>PRINCESA MARIO, DINO BEAR, GATO FRESA</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>SHORT ESQUELETO TALLA UNICA</t>
+          <t>SHORT TIRA PLUS SEDEN HASTA UNA XL</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/8nrg5mb3ft6_1784908267309.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/aeirxq4xmf_1789406213691.webp</t>
         </is>
       </c>
       <c r="P68" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>f76a5f9c-6d1c-470d-9ad3-58f6c5a4fc8a</t>
+          <t>23141b4f-2a7f-46ad-af38-1c09e3487a0a</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>STP-002</t>
+          <t>SET104</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>SHORT TIRA PLUS</t>
+          <t>SHORT ESQUELETO TALLA UNICA</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4861,7 +4861,7 @@
       <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Única</t>
         </is>
       </c>
       <c r="G69" s="3" t="n">
@@ -4886,21 +4886,21 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>PRINCESA MARIO, DINO BEAR, GATO FRESA</t>
+          <t>STICH ROSADO, STICH MORADO, STICH AZUL, STICH BLANCO</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>SHORT TIRA PLUS SEDEN HASTA UNA XL</t>
+          <t>SHORT ESQUELETO TALLA UNICA</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/aeirxq4xmf_1789406213691.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/8nrg5mb3ft6_1784908267309.jpg</t>
         </is>
       </c>
       <c r="P69" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
@@ -6228,17 +6228,17 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>ceed2bf1-60e4-41c8-a23f-372380343eea</t>
+          <t>cc4b475f-d7d8-47bd-a3d6-73439ec7046b</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>STU-001</t>
+          <t>SHD-001</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>SHORT TIRA</t>
+          <t>SHORT TIRA MUNDIALISTA</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -6249,7 +6249,7 @@
       <c r="E91" s="2" t="inlineStr"/>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Única</t>
+          <t>Única, Plus, Oversize</t>
         </is>
       </c>
       <c r="G91" s="3" t="n">
@@ -6265,7 +6265,7 @@
         <v>0</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
@@ -6274,37 +6274,37 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>OSO LOTSO, MICKEY, HELLO KITTY, TIGERS, PINGUINOS, AVOCADO, CERDITO, CAPIBARA, BAMBI, PALETA LILA, BOB ESPONJA, CINAMORROL, MINNI FLOR, ELEFANTE, STICH, OSO PANDA, MAFALDA, OVEJA NUVE, MY MELODDY</t>
+          <t>BRAZIL 2, BRAZIL, COLOMBIA 2, COLOMBIA, FRANCIA</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
+          <t>SHORT TIRA AL ESTILO MUNDIAL</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/jxcws9687y_1784922919118.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/vt26asit3lo_1784684759726.jpg</t>
         </is>
       </c>
       <c r="P91" s="2" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>cc4b475f-d7d8-47bd-a3d6-73439ec7046b</t>
+          <t>ceed2bf1-60e4-41c8-a23f-372380343eea</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>SHD-001</t>
+          <t>STU-001</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>SHORT TIRA MUNDIALISTA</t>
+          <t>SHORT TIRA</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -6315,7 +6315,7 @@
       <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Única, Plus, Oversize</t>
+          <t>Única</t>
         </is>
       </c>
       <c r="G92" s="3" t="n">
@@ -6331,7 +6331,7 @@
         <v>0</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
@@ -6340,21 +6340,21 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>BRAZIL 2, BRAZIL, COLOMBIA 2, COLOMBIA, FRANCIA</t>
+          <t>OSO LOTSO, MICKEY, HELLO KITTY, TIGERS, PINGUINOS, AVOCADO, CERDITO, CAPIBARA, BAMBI, PALETA LILA, BOB ESPONJA, CINAMORROL, MINNI FLOR, ELEFANTE, STICH, OSO PANDA, MAFALDA, OVEJA NUVE, MY MELODDY</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>SHORT TIRA AL ESTILO MUNDIAL</t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/vt26asit3lo_1784684759726.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/jxcws9687y_1784922919118.jpg</t>
         </is>
       </c>
       <c r="P92" s="2" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 00:49</t>
+          <t>2026-10-30 06:49</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 06:49</t>
+          <t>2026-10-30 12:47</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 12:47</t>
+          <t>2026-10-30 18:42</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6274,7 +6274,7 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>BRAZIL 2, BRAZIL, COLOMBIA 2, COLOMBIA, FRANCIA</t>
+          <t>BRAZIL, COLOMBIA 2, COLOMBIA, FRANCIA</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -6288,7 +6288,7 @@
         </is>
       </c>
       <c r="P91" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
@@ -6340,7 +6340,7 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>OSO LOTSO, MICKEY, HELLO KITTY, TIGERS, PINGUINOS, AVOCADO, CERDITO, CAPIBARA, BAMBI, PALETA LILA, BOB ESPONJA, CINAMORROL, MINNI FLOR, ELEFANTE, STICH, OSO PANDA, MAFALDA, OVEJA NUVE, MY MELODDY</t>
+          <t>OSO LOTSO, MICKEY, TIGERS, AVOCADO, CERDITO, BOB ESPONJA, CINAMORROL, MINNI FLOR, ELEFANTE, MAFALDA, OVEJA NUVE, MY MELODDY</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -6354,7 +6354,7 @@
         </is>
       </c>
       <c r="P92" s="2" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="93">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 18:42</t>
+          <t>2026-10-31 00:54</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-31 00:54</t>
+          <t>2026-10-31 06:45</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-31 06:45</t>
+          <t>2026-10-31 12:43</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-31 12:43</t>
+          <t>2026-10-31 18:38</t>
         </is>
       </c>
     </row>
